--- a/notebooks/Ale/feature_importance_full.xlsx
+++ b/notebooks/Ale/feature_importance_full.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -489,12 +489,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
+          <t>gd_bus</t>
         </is>
       </c>
     </row>
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0915</v>
+        <v>0.0979</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1205</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -521,23 +521,20 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0437</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1348</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.2171</v>
+        <v>0.2466</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.0467</v>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0594</v>
       </c>
     </row>
     <row r="7">
@@ -546,100 +543,103 @@
           <t>cycle_to_employer</t>
         </is>
       </c>
+      <c r="D7" t="n">
+        <v>0.1108</v>
+      </c>
       <c r="E7" t="n">
-        <v>0.1125</v>
+        <v>0.1476</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>deaths_of_enterprises</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0429</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>happiness</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0747</v>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0822</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0536</v>
+        <v>0.1903</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>net_additions</t>
+          <t>size_large_share</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0727</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.0781</v>
+        <v>0.6732</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>public_transport_to_employer</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.0654</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.0775</v>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.2635</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.1102</v>
+          <t>transport_to_employer</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>0.3531</v>
+        <v>0.0969</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>size_large_share</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.3809</v>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.08459999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>size_micro_share</t>
+          <t>within_sector_diversity</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1068</v>
+        <v>0.0164</v>
       </c>
       <c r="C15" t="n">
-        <v>0.425</v>
+        <v>0.0443</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1817</v>
       </c>
     </row>
     <row r="17">
@@ -667,12 +667,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
+          <t>gd_emp_binary</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>cagr_bus_binary</t>
+          <t>gd_bus_binary</t>
         </is>
       </c>
     </row>
@@ -683,10 +683,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0893</v>
+        <v>0.1583</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0989</v>
+        <v>0.1466</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0718</v>
       </c>
     </row>
     <row r="20">
@@ -696,142 +699,111 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1123</v>
+        <v>0.1093</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1029</v>
+        <v>0.1119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>broadband_availability</t>
-        </is>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0896</v>
       </c>
       <c r="D21" t="n">
-        <v>0.055</v>
+        <v>0.0815</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0925</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cancer_diagnosis</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.0457</v>
+          <t>drive_to_employer</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0655</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cycle_to_employer</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.0434</v>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1506</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>happiness</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.07190000000000001</v>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0948</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0399</v>
+        <v>0.061</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0618</v>
+        <v>0.1333</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1018</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>new_enterprises</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0448</v>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1676</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1839</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>reception_obesity</t>
-        </is>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.082</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0488</v>
+        <v>0.0805</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.0935</v>
+          <t>within_sector_diversity</t>
+        </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0965</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0.1532</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.1908</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>smokers</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0509</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>under_75_mortality_rate</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.0463</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>year_6_obesity</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0.0541</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.0677</v>
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -849,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -891,375 +863,670 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
+          <t>gd_bus</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>adult_obesity</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.0663</v>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2505</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0502</v>
+        <v>0.1085</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2284</v>
+        <v>0.407</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0385</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>cycle_to_employer</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1077</v>
+        <v>0.056</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4134</v>
+        <v>0.0636</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cycle_to_employer</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0484</v>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0558</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.0428</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.078</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
-        </is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0761</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0612</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0399</v>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>net_additions</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.048</v>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.08119999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>public_transport_to_employer</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.1074</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.09329999999999999</v>
+          <t>related_variety</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>0.053</v>
+        <v>0.0497</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.07679999999999999</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.4138</v>
+          <t>size_large_share</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2959</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>size_large_share</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.5017</v>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0751</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.1114</v>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0438</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>smokers</t>
+          <t>within_sector_diversity</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0304</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>worthwhile</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.0357</v>
+        <v>0.4197</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>cagr_bus_binary</t>
-        </is>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1621</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.2376</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0556</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>adult_obesity</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0772</v>
+        <v>0.2114</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>anxiety</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.0435</v>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0842</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.0944</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.1385</v>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.07190000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.1017</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.2109</v>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.059</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cycle_to_employer</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0454</v>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.0854</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0935</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.0536</v>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0833</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0832</v>
+        <v>0.1632</v>
       </c>
       <c r="C27" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.058</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0.1064</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.093</v>
+          <t>related_variety</t>
+        </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0478</v>
+        <v>0.0629</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>net_additions</t>
-        </is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.0872</v>
       </c>
       <c r="D29" t="n">
-        <v>0.044</v>
+        <v>0.1494</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>new_enterprises</t>
-        </is>
+          <t>within_sector_diversity</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0588</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0445</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.1505</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>size_large_share</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0.0762</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.0533</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>smokers</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0.043</v>
+        <v>0.1986</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sector: Defence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>REGRESSION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>lq_emp</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>lq_bus</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>gd_emp</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>gd_bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2422</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1044</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0727</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>drive_to_employer</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0636</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1039</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0677</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0668</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2559</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.119</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4518</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1664</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1245</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.07439999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1292</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1312</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0601</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0688</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.2137</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.08110000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1257</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1255</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1028</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A15:E15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1278,7 +1545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sector: Defence</t>
+          <t>Sector: Digital and Technologies</t>
         </is>
       </c>
     </row>
@@ -1307,309 +1574,339 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
+          <t>gd_bus</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4g_area_coverage</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.07580000000000001</v>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1694</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>anxiety</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.0238</v>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2565</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0586</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0761</v>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0645</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0548</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.3436</v>
+        <v>0.0511</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1234</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1597</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.3123</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0742</v>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cancer_diagnosis</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3439</v>
+        <v>0.0819</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0491</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>deaths_of_enterprises</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0687</v>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0833</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>early_years_comms</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3477</v>
+        <v>0.0765</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2075</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
-        </is>
+          <t>size_large_share</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5441</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1052</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0984</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
-        </is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0697</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1007</v>
+        <v>0.2303</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>within_sector_diversity</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.0789</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>net_additions</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.1149</v>
+        <v>0.0573</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.199</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>smokers</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.0741</v>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
-        </is>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0599</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>cagr_bus_binary</t>
-        </is>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.139</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.1092</v>
+          <t>cycle_to_employer</t>
+        </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2021</v>
+        <v>0.0675</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0672</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.09520000000000001</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.1337</v>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1052</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>broadband_availability</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0618</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.0539</v>
+        <v>0.1112</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cancer_diagnosis</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.0732</v>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1101</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>early_years_maths</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0445</v>
+        <v>0.0921</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1714</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.0677</v>
+          <t>size_large_share</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.1845</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0728</v>
+        <v>0.0944</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
-        </is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1362</v>
       </c>
       <c r="D26" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0.0604</v>
+          <t>transport_to_employer</t>
+        </is>
       </c>
       <c r="D27" t="n">
-        <v>0.0518</v>
+        <v>0.0595</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>new_enterprises</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.07489999999999999</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.0589</v>
+          <t>within_sector_diversity</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1354</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A16:E16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1622,7 +1919,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sector: Digital and Technologies</t>
+          <t>Sector: Financial Services</t>
         </is>
       </c>
     </row>
@@ -1651,360 +1948,346 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
+          <t>gd_bus</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>active_enterprises</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0517</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0751</v>
+        <v>0.06909999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.1736</v>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.094</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.224</v>
+          <t>coverage_4g</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06809999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>early_years_maths</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.042</v>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1511</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
-        </is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2845</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2794</v>
+        <v>0.1239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.1026</v>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1112</v>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0362</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2465</v>
+        <v>0.0585</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0382</v>
+        <v>0.0415</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1447</v>
+        <v>0.1934</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3038</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>net_additions</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.0484</v>
+          <t>size_large_share</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6018</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0583</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0898</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0604</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.1665</v>
+        <v>0.0313</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>size_large_share</t>
+          <t>within_sector_diversity</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5516</v>
+        <v>0.0384</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0864</v>
+        <v>0.2629</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0503</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.0433</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1206</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0644</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>cagr_bus_binary</t>
-        </is>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0847</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.07439999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>adult_obesity</t>
+          <t>drive_to_employer</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0699</v>
+        <v>0.0716</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0885</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.09660000000000001</v>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1339</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.0594</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0975</v>
+        <v>0.1591</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.184</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>deaths_of_enterprises</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0519</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.0489</v>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0668</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0765</v>
+        <v>0.0844</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1044</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.0552</v>
+        <v>0.0911</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0596</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0644</v>
+          <t>size_large_share</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.1727</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0654</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.1353</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>net_additions</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.0736</v>
+        <v>0.0617</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>new_enterprises</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0495</v>
+        <v>0.08550000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.1457</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>size_large_share</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0.1666</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.06950000000000001</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0.0951</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0594</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.0638</v>
+          <t>within_sector_diversity</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1049</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A16:E16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2017,7 +2300,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sector: Financial Services</t>
+          <t>Sector: Life Sciences</t>
         </is>
       </c>
     </row>
@@ -2046,105 +2329,114 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
+          <t>gd_bus</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4g_area_coverage</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0511</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.06560000000000001</v>
+          <t>apprenticeship_starts</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>anxiety</t>
+          <t>cycle_to_employer</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.0785</v>
+        <v>0.0854</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.06909999999999999</v>
+          <t>drive_to_employer</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.043</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>drive_to_employer</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.0583</v>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0902</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0167</v>
+        <v>0.1303</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1182</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.3366</v>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0907</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>net_additions</t>
+          <t>housing_net_additions</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0547</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0916</v>
+        <v>0.1099</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>reception_obesity</t>
-        </is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0728</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0614</v>
+        <v>0.0941</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0546</v>
       </c>
     </row>
     <row r="12">
@@ -2154,259 +2446,222 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0455</v>
+        <v>0.1138</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1595</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1863</v>
+        <v>0.0764</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>size_large_share</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7526</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.0481</v>
+        <v>0.1611</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.016</v>
+          <t>within_sector_diversity</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4041</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1188</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>under_75_mortality_rate</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0.0451</v>
+        <v>0.4431</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>cagr_bus_binary</t>
-        </is>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0838</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4g_area_coverage</t>
+          <t>broadband</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0725</v>
+        <v>0.0731</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>adult_obesity</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.051</v>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1089</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cancer_diagnosis</t>
-        </is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.1134</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1039</v>
+        <v>0.0752</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1005</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cycle_to_employer</t>
-        </is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.1114</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0674</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.0432</v>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.064</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.06510000000000001</v>
+          <t>nvq_level3</t>
+        </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1106</v>
+        <v>0.0578</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0442</v>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.119</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>new_enterprises</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0482</v>
+        <v>0.148</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.09669999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>reception_obesity</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0.06569999999999999</v>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0711</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0.0478</v>
+          <t>within_sector_diversity</t>
+        </is>
       </c>
       <c r="C28" t="n">
-        <v>0.09859999999999999</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>size_large_share</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0.2468</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.1012</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0.1299</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.0466</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.0605</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>under_75_mortality_rate</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.0795</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>year_6_obesity</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0.0558</v>
+        <v>0.2474</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0751</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A16:E16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2419,7 +2674,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sector: Life Sciences</t>
+          <t>Sector: Professional and Business Services</t>
         </is>
       </c>
     </row>
@@ -2448,757 +2703,320 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>cagr_emp</t>
+          <t>gd_emp</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>cagr_bus</t>
+          <t>gd_bus</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>active_enterprises</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0511</v>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0362</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>anxiety</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.0765</v>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2452</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1139</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.0883</v>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>deaths_of_enterprises</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0848</v>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1054</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0992</v>
+        <v>0.1752</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2478</v>
+        <v>0.0822</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1101</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0506</v>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1218</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1809</v>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0776</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>life_satisfaction</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.1102</v>
+          <t>size_large_share</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2534</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>new_enterprises</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.0588</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.0994</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.0725</v>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0537</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>within_sector_diversity</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2987</v>
+        <v>0.1349</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2866</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.1317</v>
+        <v>0.1631</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>under_75_mortality_rate</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.0675</v>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>worthwhile</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.1607</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.0832</v>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0799</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1452</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
-        </is>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0535</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>cagr_bus_binary</t>
-        </is>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>drive_to_employer</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.06320000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>anxiety</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.0451</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.0617</v>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0935</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>deaths_of_enterprises</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.05</v>
+          <t>enterprise_high_growth_rate</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>0.0452</v>
+        <v>0.1525</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0597</v>
+        <v>0.1252</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0492</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.0674</v>
+        <v>0.1348</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0496</v>
+        <v>0.0837</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
-        </is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.1157</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0485</v>
+        <v>0.2356</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0422</v>
+        <v>0.0772</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.0609</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0907</v>
+          <t>size_large_share</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.08550000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.2527</v>
+          <t>size_micro_share</t>
+        </is>
       </c>
       <c r="E25" t="n">
-        <v>0.1103</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0.0832</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.1832</v>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>smokers</t>
-        </is>
+          <t>within_sector_diversity</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1095</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>under_75_mortality_rate</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.0444</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>worthwhile</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.0573</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>year_6_obesity</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0.0521</v>
+        <v>0.1308</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A18:E18"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Sector: Professional and Business Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>REGRESSION</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>lq_emp</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>lq_bus</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>cagr_emp</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>cagr_bus</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>active_enterprises</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.06279999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adult_obesity</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.0448</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.3673</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.07679999999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.1729</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.1486</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>early_years_literacy</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.0664</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>gcse_by_age_19</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.07679999999999999</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.0432</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.1709</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0896</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.0557</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>public_transport_to_employer</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.0672</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>reception_obesity</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1711</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.1141</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0505</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.1602</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>size_large_share</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.2523</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0658</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>smokers</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.051</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>cagr_bus_binary</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>4g_area_coverage</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.0477</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adult_obesity</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.08690000000000001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.0893</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.1359</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.0539</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cycle_to_employer</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0437</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>early_years_literacy</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.0482</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>fe_and_skills_participation</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.0441</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>gcse_by_age_19</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0.1372</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.07729999999999999</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0.0557</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.1362</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>0.1181</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>size_large_share</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0.0939</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0.0588</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.081</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>under_75_mortality_rate</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.0427</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>year_6_obesity</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>0.0565</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
